--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -688,7 +688,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; CASE_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RETURN_002; RELOC_005</t>
+          <t>RETURN_001; CASE_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; TRD_001; RETURN_001; RELOC_005</t>
+          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; RETURN_001; TRD_001; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>WH_001; RETURN_001; RETURN_004</t>
+          <t>WH_001; RETURN_001; RELOC_005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; RETURN_001; RELOC_001; TRD_003; RETURN_004</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; RETURN_001; RELOC_001; TRD_003; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; RELOC_001; CASE_010; WTO_001; RELOC_005</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; RELOC_001; RETURN_002; CASE_010; WTO_001</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RETURN_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004</t>
+          <t>RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; TRD_001</t>
+          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; RETURN_001</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; RETURN_001; RELOC_001; RELOC_005</t>
+          <t>TRD_003; CASE_002; RETURN_001; RELOC_001; RETURN_002</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; WH_002</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_002; RELOC_003; RELOC_001; PLUS1_003; CASE_005; CASE_004; CASE_001; CASE_006</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; CASE_002; TRD_003; WH_002</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010; WH_002; CASE_003; CASE_002; TRD_003; TRD_001</t>
+          <t>CASE_007; CASE_010; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -683,12 +683,16 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; CSIS_001</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; CASE_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; CASE_002; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -729,12 +733,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_003; RELOC_004; RELOC_006; RETURN_001; RETURN_004; RELOC_001; RELOC_002; RELOC_008; RELOC_007</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_003; RELOC_004; RELOC_006; RETURN_001; RETURN_004; RELOC_001; RELOC_002; RELOC_008; RELOC_007</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -785,12 +789,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_001; RELOC_002; RELOC_006; RETURN_004</t>
+          <t>WH_002; WTO_001; CASE_001; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_002; RELOC_004; RELOC_006; RETURN_004</t>
+          <t>CASE_003; CASE_002; DOC_001; WH_002; WTO_001; CASE_001; CASE_010; CASE_008; CASE_007; TRD_001</t>
         </is>
       </c>
     </row>
@@ -816,13 +820,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -837,12 +841,16 @@
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; FR_001; ITA_001; RETURN_001; RELOC_006; WH_002</t>
+          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; FR_001; ITA_001; WH_002; CSIS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -949,12 +957,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; CSIS_001; MOFCOM_001</t>
+          <t>CSIS_001; MOFCOM_001; WH_001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; FR_001; MOFCOM_002; RETURN_001; CSIS_001; WH_002; MOFCOM_001</t>
+          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; CSIS_001; WH_002; MOFCOM_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; RETURN_001; TRD_001; RELOC_005</t>
+          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; TRD_001; TRD_002; CASE_009</t>
         </is>
       </c>
     </row>
@@ -1036,13 +1044,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1057,16 +1065,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>WH_001; RETURN_001; RELOC_005</t>
+          <t>WH_001; CSIS_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; RETURN_001; RELOC_001; TRD_003; RELOC_005</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_003; WH_001; TRD_001; ITA_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1092,13 +1100,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1113,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001</t>
+          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; WTO_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; IMF_001; CNGOV_001; UNCTAD_001; RETURN_004; RELOC_004; PLUS1_001; RELOC_006; RELOC_005; PLUS1_002</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; TRD_003; WTO_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1171,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1217,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; RETURN_001; IMF_001; WTO_001; WEF_001; MCK_001; CNGOV_001; TRD_003; RELOC_007</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; RETURN_001; IMF_001; WTO_001; WEF_001; MCK_001; CNGOV_001; TRD_003; RELOC_007</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1278,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; WH_002; MOFCOM_002; CASE_003; TRD_001</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; WH_002; CASE_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1360,41 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>China; EV Battery; Malaysia; Thailand; United States; Vietnam</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; RETURN_001; TRD_003; RELOC_001; RELOC_005; WH_002; TRD_002</t>
+          <t>TRD_001; TRD_003; WH_002; CASE_003; TRD_002; CASE_002; CASE_010; CSIS_001; CASE_007; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1404,13 +1420,13 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1425,12 +1441,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>WTO_001; CSIS_001; WH_001</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; RELOC_005; RELOC_003; CASE_010; WH_002; RETURN_004; RELOC_002; RELOC_008; RELOC_004; RELOC_001</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; TRD_001; CASE_002; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1456,13 +1476,13 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1477,12 +1497,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; CASE_001; WTO_001; TRD_002; CSIS_001</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001; RELOC_001; RELOC_008; RELOC_007; RELOC_003; PLUS1_002</t>
+          <t>TRD_003; CASE_002; CASE_008; WH_002; TRD_001; CASE_001; MOFCOM_001; WTO_001; TRD_002; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1547,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; RELOC_005; RELOC_001; PLUS1_001; RETURN_004; RELOC_006; CASE_001; RELOC_003; RELOC_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_007; CASE_003; CASE_006; CASE_005; WH_002; CASE_002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; RELOC_005; RELOC_001; PLUS1_001; RETURN_004; RELOC_006; CASE_001; RELOC_003; RELOC_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_007; CASE_003; CASE_006; CASE_005; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1554,13 +1578,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1575,16 +1599,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WH_001; WTO_001</t>
+          <t>WTO_001; WH_001; CSIS_001; CASE_002</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; WH_001; WTO_001; RETURN_004; TRD_001; RELOC_006; RELOC_002</t>
+          <t>TRD_003; WH_002; CASE_010; WTO_001; WH_001; TRD_001; CSIS_001; CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -1610,13 +1634,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1631,16 +1655,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001; RETURN_001</t>
+          <t>CSIS_001; WH_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; RELOC_005; CASE_003; TRD_001; RETURN_001</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002; ITA_001</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1720,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; WH_002; RETURN_001; MOFCOM_001; CASE_010; CASE_003; RELOC_006; CASE_002</t>
+          <t>BIS_001; BIS_002; CASE_009; WH_002; CASE_010; CASE_003; MOFCOM_001; CASE_001; CASE_002; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -1722,13 +1746,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1743,16 +1767,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CSIS_001; WH_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; RELOC_005; RELOC_002; RELOC_001; RELOC_006</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; CASE_009</t>
         </is>
       </c>
     </row>
@@ -1778,13 +1802,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0.4</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1799,16 +1823,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>WH_001; RELOC_005; CSIS_001; RELOC_002; RETURN_001; RELOC_006</t>
+          <t>WH_001; CSIS_001; CASE_008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_005; CSIS_001; RELOC_002; RETURN_001; RELOC_004; RELOC_006; RELOC_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1873,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; PLUS1_002; RETURN_001; RETURN_004; PLUS1_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; PLUS1_002; RETURN_001; RETURN_004; PLUS1_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1880,13 +1904,13 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1901,16 +1925,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; WH_002; CASE_001; RELOC_006; MOFCOM_002; CASE_003; RETURN_001</t>
+          <t>BIS_002; BIS_001; CASE_009; FR_001; WH_002; CASE_001; MOFCOM_002; CASE_003; WTO_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1990,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; RELOC_005; WH_001; CSIS_001; RETURN_001</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1992,13 +2016,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2013,16 +2037,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; WTO_001</t>
+          <t>DOC_001; CASE_003; WTO_001; CSIS_001; WH_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; RELOC_001; RETURN_002; CASE_010; WTO_001</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; WTO_001; CSIS_001; WH_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2087,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; RETURN_001; WEF_001; PLUS1_001; RELOC_001; MCK_001; RELOC_005</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; RETURN_001; WEF_001; PLUS1_001; RELOC_001; MCK_001; RELOC_005</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; WH_001; RELOC_006; RELOC_004; RELOC_002; TRD_001; CASE_003; CSIS_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; TRD_001; CSIS_001; CASE_002; TRD_003; TRD_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2230,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_002; RELOC_003; RELOC_001; PLUS1_003</t>
+          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2258,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_002; RELOC_003; RELOC_001; PLUS1_003</t>
+          <t>CASE_005; CASE_004; CASE_006; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2286,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_002; TRD_003</t>
+          <t>CASE_007; CASE_002; TRD_003; TRD_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2314,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010; WH_002</t>
+          <t>CASE_007; CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2346,7 +2370,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RELOC_004; PLUS1_004; CASE_010; WH_002; CASE_003; CASE_002</t>
+          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2370,11 +2394,11 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2398,11 +2422,11 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2454,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RETURN_001; CASE_001; RETURN_003; RELOC_006; RELOC_003; RELOC_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2482,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RETURN_001; RELOC_004</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2538,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_001; MOFCOM_002; RETURN_001; RELOC_006</t>
+          <t>MOFCOM_001; MOFCOM_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2566,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; RETURN_001; RELOC_006</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2734,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; FR_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001</t>
         </is>
       </c>
     </row>
@@ -2734,11 +2758,11 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; RETURN_001</t>
+          <t>CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2762,11 +2786,11 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; TRD_003; TRD_001</t>
+          <t>CASE_010; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2846,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_001</t>
+          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2846,11 +2870,11 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; TRD_001</t>
+          <t>CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2930,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; RELOC_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2958,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RETURN_001; CNGOV_001; RETURN_004; RELOC_004; PLUS1_001; RELOC_006</t>
+          <t>CNGOV_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2986,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; WH_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3070,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; RETURN_001; TRD_003</t>
+          <t>TRD_001; TRD_003; CASE_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3067,16 +3091,9 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>RELOC_006; RELOC_003; RELOC_004; RETURN_001; RELOC_001; RELOC_005</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3102,7 +3119,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_004; RETURN_001; TRD_003; WH_002; TRD_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; CASE_010; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3147,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; TRD_003; RELOC_001; WH_002</t>
+          <t>TRD_001; TRD_003; TRD_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3175,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_004; RELOC_001; WH_002; TRD_002</t>
+          <t>TRD_001; WH_002; CASE_003; TRD_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3203,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_003; TRD_003; RELOC_005; WH_002; TRD_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3231,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; RELOC_005; RELOC_003; RETURN_004; RELOC_002; RELOC_008</t>
+          <t>TRD_003; TRD_001; CASE_002; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3287,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001; RELOC_001</t>
+          <t>TRD_003; CASE_002; CASE_008; TRD_001; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3315,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; TRD_001</t>
+          <t>TRD_003; CASE_010; TRD_001; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3343,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_004; TRD_001; RELOC_006</t>
+          <t>TRD_003; CASE_010; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3399,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003</t>
+          <t>CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3455,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3483,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; TRD_003; RELOC_005; CASE_003</t>
+          <t>CASE_010; TRD_003; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3490,11 +3507,11 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_006; CASE_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3595,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003</t>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3623,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; WH_002; CASE_010; RELOC_002; RELOC_001</t>
+          <t>DOC_001; CASE_010; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3651,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; RELOC_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3679,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; RELOC_005</t>
+          <t>DOC_001; CASE_003; CASE_010; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3707,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002</t>
+          <t>CASE_010; WH_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3735,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RELOC_004; RELOC_001</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3847,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; RETURN_001</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3875,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; RELOC_005; RETURN_001</t>
+          <t>CASE_002; TRD_003; CASE_008; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3931,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3959,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; RETURN_001; RELOC_001; RETURN_002</t>
+          <t>TRD_003; CASE_002; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3998,7 +4015,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; RELOC_004; TRD_001; CASE_003</t>
+          <t>CASE_010; CASE_003; TRD_001; TRD_003; TRD_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4043,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RELOC_006; RELOC_002; TRD_001</t>
+          <t>CASE_010; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4071,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002</t>
+          <t>CASE_010; WH_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4099,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RELOC_004; TRD_001; CASE_003</t>
+          <t>CASE_010; WH_002; CASE_003; TRD_001; CASE_002; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4147,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -4145,7 +4162,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -4160,7 +4177,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.825</v>
+        <v>0.754</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4205,7 +4222,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -4220,7 +4237,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -4250,7 +4267,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -4316,7 +4333,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; WH_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; CASE_002; TRD_003; WH_002</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; EU_003; CASE_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
+          <t>CASE_007; CASE_010; CASE_003; WH_002; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CSIS_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; CASE_002; CSIS_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>WH_002; WTO_001; CASE_001; CASE_010; TRD_001</t>
+          <t>CASE_001; CASE_010; WH_002; CSIS_001; KPMG_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; WH_002; WTO_001; CASE_001; CASE_010; CASE_008; CASE_007; TRD_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_001; CASE_010; WH_002; CASE_008; CASE_007; CSIS_001; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; FR_001; ITA_001; WH_002; CSIS_001; CASE_002</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; FR_001; ITA_001; IRS_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; WH_002; CASE_002; CSIS_001; CASE_003; WH_001</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; WH_002; CSIS_001; CASE_002; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; MOFCOM_001; WH_001</t>
+          <t>CSIS_001; UST_001; EU_003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; CSIS_001; WH_002; MOFCOM_001; WH_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; MOFCOM_002; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; TRD_001; TRD_002; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; TRD_002; UST_001</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1065,16 +1065,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_003; WH_001; TRD_001; ITA_001; CSIS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; WH_002; ITA_001; CSIS_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; WTO_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; WH_002</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; TRD_003; WTO_001; TRD_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; IRS_001; WH_002; EU_003</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; WH_002; CASE_003; TRD_001</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002; MOFCOM_001; CASE_003; IRS_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002; CASE_002; CSIS_001; CASE_003; MOFCOM_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002; UST_001; CASE_002; CSIS_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -1360,41 +1360,37 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>China; EV Battery; Malaysia; Thailand; United States; Vietnam</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>EV Battery</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001; CSIS_001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; CASE_003; TRD_002; CASE_002; CASE_010; CSIS_001; CASE_007; CASE_001</t>
+          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; UST_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1441,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; WH_001</t>
+          <t>CSIS_001; WTO_001; UST_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; TRD_001; CASE_002; CASE_008; CASE_007</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; WH_001; CASE_002; CASE_008; UST_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1476,13 +1472,13 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1497,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_001; WTO_001; TRD_002; CSIS_001</t>
+          <t>WH_002; CASE_001; CSIS_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; WH_002; TRD_001; CASE_001; MOFCOM_001; WTO_001; TRD_002; CSIS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; WH_002; CASE_001; TRD_001; EU_003; CSIS_001; CASE_007; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1578,13 +1574,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1599,16 +1595,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; WH_001; CSIS_001; CASE_002</t>
+          <t>WTO_001; CSIS_001; CASE_002; UST_001; EU_003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WTO_001; WH_001; TRD_001; CSIS_001; CASE_002; CASE_003; TRD_002</t>
+          <t>TRD_003; WH_002; WH_001; WTO_001; CSIS_001; TRD_001; CASE_002; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1634,13 +1630,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1655,16 +1651,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002; ITA_001</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; FR_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1711,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; WH_002; CASE_010; CASE_003; MOFCOM_001; CASE_001; CASE_002; MOFCOM_002</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_010; UST_001; CASE_003; WH_002; EU_003</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1767,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001; EU_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; CASE_009</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1823,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001; CASE_008</t>
+          <t>CSIS_001; CASE_008; EU_001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_009; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1869,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1930,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; WH_002; CASE_001; MOFCOM_002; CASE_003; WTO_001; CSIS_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; WH_002; CASE_003; CASE_010; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1960,13 +1956,13 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1981,16 +1977,16 @@
         <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2016,13 +2012,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2037,16 +2033,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; WTO_001; CSIS_001; WH_001</t>
+          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; WTO_001; CSIS_001; WH_001; CASE_008</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WTO_001; WH_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2083,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
+          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
+          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2114,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2139,16 +2135,16 @@
         <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; TRD_001; CSIS_001; CASE_002; TRD_003; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2310,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_007; CASE_010; CASE_003; WH_002; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2366,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; TRD_002</t>
+          <t>CASE_010; CASE_003; WH_002; CASE_002; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; CASE_002</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2450,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2506,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009</t>
+          <t>BIS_002; BIS_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -2534,11 +2530,11 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_001; MOFCOM_002; CASE_002</t>
+          <t>MOFCOM_002; MOFCOM_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2562,11 +2558,11 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_002; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2590,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; MOFCOM_002; FR_001; ITA_001</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; FR_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2618,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002</t>
+          <t>CASE_009; BIS_002; BIS_001</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2678,7 +2674,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; WH_002</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2730,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; MOFCOM_002; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2758,11 +2754,11 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2786,11 +2782,11 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2814,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2842,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2870,11 +2866,11 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003</t>
+          <t>CASE_010; WH_001; WH_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2926,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; TRD_003; TRD_001</t>
+          <t>CNGOV_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3010,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>FR_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3066,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_002; CASE_007</t>
+          <t>TRD_001; TRD_003; CASE_002; IRS_001</t>
         </is>
       </c>
     </row>
@@ -3091,9 +3087,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3119,7 +3122,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; CASE_010; CASE_007</t>
+          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3150,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; CASE_010</t>
+          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3178,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; WH_002; CASE_003; TRD_002; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_002; WH_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3206,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3234,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; TRD_001; CASE_002; CASE_008; CASE_007</t>
+          <t>TRD_003; CASE_002; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3262,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3290,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; MOFCOM_001</t>
+          <t>CASE_002; TRD_003; CASE_008; TRD_001; EU_003; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3318,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; TRD_001; CASE_003; TRD_002</t>
+          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3346,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; TRD_001; TRD_002</t>
+          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3374,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010</t>
+          <t>TRD_003; WH_002; WH_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3430,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3458,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3486,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_003; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3507,11 +3510,11 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>EU_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3542,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; WH_002; CASE_010; CASE_003</t>
+          <t>BIS_001; BIS_002; CASE_009; IRS_001; CASE_010; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3570,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003</t>
+          <t>CASE_002; DOC_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3598,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3619,11 +3622,11 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_010; TRD_001; TRD_002</t>
+          <t>DOC_001; CASE_010; WH_002; TRD_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3654,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3678,11 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CASE_010; TRD_001; TRD_002</t>
+          <t>DOC_001; CASE_003; CASE_010; WH_002; TRD_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3710,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3738,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; CASE_009</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3766,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009</t>
+          <t>BIS_002; CASE_009; BIS_001</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3794,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3822,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; WH_002; CASE_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3850,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_008</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3903,7 +3906,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3934,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3990,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4018,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_001; TRD_003; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4046,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_001; TRD_003; TRD_002</t>
+          <t>CASE_010; WH_002; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4074,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4102,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; TRD_001; CASE_002; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4150,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -4162,7 +4165,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -4177,7 +4180,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.754</v>
+        <v>0.783</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4222,7 +4225,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4270,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -4333,7 +4336,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; IEA_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; EU_003; CASE_002; TRD_003</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; IEA_001; CASE_008; CASE_007; WB_001; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -631,12 +631,16 @@
         <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; WH_002; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
+          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -687,12 +691,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; EU_003; UST_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; IEA_001; SNE_001; TSLA_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -733,12 +737,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
     </row>
@@ -764,13 +768,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -785,16 +789,16 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_010; WH_002; CSIS_001; KPMG_001</t>
+          <t>DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_001; CASE_010; WH_002; CASE_008; CASE_007; CSIS_001; KPMG_001</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -820,13 +824,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -841,16 +845,12 @@
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; FR_001; ITA_001; IRS_001; EU_003; UST_001</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,12 @@
         <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001; UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; WH_002; CSIS_001; CASE_002; IRS_001; UST_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001; XPEV_001; USMCA_001; NIO_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -932,13 +928,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -953,16 +949,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; UST_001; EU_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; MOFCOM_002; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
+          <t>BIS_002; CASE_009; BIS_001; ITA_001; FR_001; MOFCOM_002; NIO_001; DHS_001; XPEV_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -988,13 +984,13 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1009,16 +1005,12 @@
         <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001; UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; TRD_002; UST_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; USMCA_001; TRD_001; DHS_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1036,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1065,16 +1057,12 @@
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; WH_002; ITA_001; CSIS_001; TRD_003; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; TRD_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1100,13 +1088,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1121,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; WH_002</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001; MCK_001; WEF_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; IRS_001; WH_002; EU_003</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001; MCK_001; IRS_001; WEF_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1159,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
+          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
+          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1205,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1266,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002; MOFCOM_001; CASE_003; IRS_001; WH_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; FR_001; XPEV_001; MOFCOM_001; DHS_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1304,13 +1292,13 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1325,16 +1313,12 @@
         <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002; UST_001; CASE_002; CSIS_001; MOFCOM_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; XPEV_001; WH_002; UST_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1360,13 +1344,13 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1381,16 +1365,12 @@
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>UST_001; CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; UST_001; CSIS_001</t>
+          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1421,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WTO_001; UST_001</t>
+          <t>WTO_001; DHS_001; UST_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; WH_001; CASE_002; CASE_008; UST_001; CASE_007</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; DHS_001; USMCA_001; WH_001; UST_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1477,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_001; CSIS_001</t>
+          <t>DHS_001; TSLA_001; CASE_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; WH_002; CASE_001; TRD_001; EU_003; CSIS_001; CASE_007; IRS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; EU_003; TSLA_001; TRD_001; CASE_001; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1523,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_007; CASE_003; CASE_006; CASE_005; WH_002; CASE_002</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_007; CASE_003; CASE_006; CASE_005; WH_002; CASE_002</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
         </is>
       </c>
     </row>
@@ -1574,13 +1554,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1595,16 +1575,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; CASE_002; UST_001; EU_003</t>
+          <t>WTO_001; DHS_001; IEA_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WH_001; WTO_001; CSIS_001; TRD_001; CASE_002; CASE_010; UST_001; EU_003</t>
+          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1630,13 +1610,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1651,16 +1631,12 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; FR_001; TRD_002</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1692,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_010; UST_001; CASE_003; WH_002; EU_003</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1742,13 +1718,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1763,16 +1739,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; EU_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; DHS_001; EU_001</t>
         </is>
       </c>
     </row>
@@ -1798,13 +1774,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1819,16 +1795,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; CASE_008; EU_001</t>
+          <t>EU_001; CASE_008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_009; CASE_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; USMCA_001; EU_001; CASE_008; CASE_003; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1845,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1900,13 +1876,13 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1921,16 +1897,12 @@
         <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; WH_002; CASE_003; CASE_010; CSIS_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; DHS_001; NIO_001; CASE_001; XPEV_001; MOFCOM_002; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1956,13 +1928,13 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1977,16 +1949,12 @@
         <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; TRD_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; USMCA_001; CASE_008; CASE_010</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2005,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
+          <t>CASE_003; DOC_001; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WTO_001; WH_001; CASE_008</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2051,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -2114,13 +2082,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2135,16 +2103,558 @@
         <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; TRD_003; USMCA_001; CASE_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery; Tariff</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; CSIS_001</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; IRS_001; LI_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Tariff; United States</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_001</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002; CASE_009; BIS_001; MOFCOM_001; TSLA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery; Mexico; Tariff; Transshipment</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>WTO_001</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; WTO_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>India; Tariff</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; CASE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>EV Battery; Indonesia</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; EU_003; WTO_002; MOFCOM_002; TSLA_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>China; Indonesia; Mexico; Vietnam</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; TSLA_001; CSIS_001</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; DHS_001; TRD_001; CASE_002; SNE_001; IEA_001; TSLA_001; ALB_001; EU_003; CSIS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>EV Battery; United States</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002; UST_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001; UST_001; WH_002</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; ALB_001; IEA_001; CSIS_001; IRS_001; UST_001; TSLA_001; WH_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>China; Indonesia; Mexico; Transshipment</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; EU_001</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; WH_002; WTO_004; DHS_001; CASE_002; EU_003; EU_001; EU_002</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2226,7 +2736,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; TRD_001</t>
+          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; WB_001</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2764,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_006; TRD_001; TRD_003</t>
+          <t>CASE_005; CASE_004; CASE_006; WB_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2792,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_002; TRD_003; TRD_001; CASE_008</t>
+          <t>CASE_007; CASE_002; TRD_003; TRD_001; WB_001</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2820,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; WH_002; TRD_003; TRD_001</t>
+          <t>CASE_007; CASE_010; WH_002; CASE_003; CASE_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2876,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; WH_002; CASE_002; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; WB_001</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2904,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2932,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; SNE_001</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2960,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_001; EU_003; UST_001</t>
+          <t>CASE_001; TSLA_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2988,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2534,7 +3044,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_002; MOFCOM_001; IRS_001; EU_003</t>
+          <t>MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2562,7 +3072,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; IRS_001; EU_003</t>
+          <t>MOFCOM_002; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2590,7 +3100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; FR_001; ITA_001</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -2618,7 +3128,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001</t>
+          <t>CASE_009; BIS_001; BIS_002</t>
         </is>
       </c>
     </row>
@@ -2642,11 +3152,11 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_001; ITA_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -2674,7 +3184,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; WH_002</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -2730,7 +3240,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; MOFCOM_002; ITA_001</t>
+          <t>BIS_002; CASE_009; BIS_001; ITA_001; FR_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2758,7 +3268,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_003; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2786,7 +3296,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_001; TRD_003; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3324,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2842,7 +3352,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2870,7 +3380,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_003; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2898,7 +3408,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; WH_002; TRD_003</t>
+          <t>CASE_010; WH_001; USMCA_001; WH_002; TRD_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -2926,7 +3436,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2954,7 +3464,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; IRS_001; EU_003</t>
+          <t>CNGOV_001; SNE_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3492,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3548,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3576,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_002; IRS_001</t>
+          <t>TRD_001; TRD_003; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3600,11 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>DHS_001; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3632,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_010</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3660,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_010</t>
+          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3688,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; WH_002; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; DHS_001; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3716,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_010</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3744,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; CASE_007</t>
+          <t>TRD_003; USMCA_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3772,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3800,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; TRD_001; EU_003; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; EU_003; TRD_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3884,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WH_001; CASE_010</t>
+          <t>TRD_003; WH_002; CSIS_001; USMCA_001; WH_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3398,11 +3908,11 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; TRD_002</t>
+          <t>CSIS_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3940,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3968,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3996,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3514,7 +4024,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EU_001; IRS_001; EU_003</t>
+          <t>DHS_001; EU_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3542,7 +4052,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; IRS_001; CASE_010; CASE_003</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; XPEV_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3598,7 +4108,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -3622,11 +4132,11 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_010; WH_002; TRD_002; TRD_001</t>
+          <t>CASE_002; DOC_001; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3654,7 +4164,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3678,11 +4188,11 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CASE_010; WH_002; TRD_002; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3710,7 +4220,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3738,7 +4248,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3822,7 +4332,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; DHS_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3850,7 +4360,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_008</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3874,11 +4384,11 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; TRD_001</t>
+          <t>CASE_002; TRD_003; USMCA_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3906,7 +4416,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>WH_002; TRD_003; WH_001; CSIS_001; USMCA_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3934,7 +4444,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; WH_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -3962,7 +4472,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008</t>
+          <t>TRD_003; CASE_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4500,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001</t>
+          <t>TRD_003; WH_002; CASE_010; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4528,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4556,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4584,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4612,740 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_002; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>EU_003; SNE_001; IRS_001; LI_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; DHS_001; SNE_001; IEA_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; UST_001; LI_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FR_001; TSLA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>USMCA_001; CASE_002; EU_003; IRS_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>USMCA_001; CASE_002; DHS_001; EU_003; IRS_001; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>USMCA_001; UST_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Transshipment</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>USMCA_001; WH_002; CSIS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; IEA_001; CASE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; UST_001; CASE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; EU_003; WTO_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>WB_001; TRD_001; CASE_002; SNE_001; ALB_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>WB_001; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>WB_001; TRD_001; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; TSLA_001; BIS_001; USMCA_001; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SNE_001; EU_003; ALB_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; ALB_001; IEA_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; EU_003; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>WB_001; WH_002; WTO_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Transshipment</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>USMCA_001; WH_002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4150,11 +5388,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.892</v>
+        <v>0.92</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mean over 24 entity-bearing questions</t>
+          <t>mean over 33 entity-bearing questions</t>
         </is>
       </c>
     </row>
@@ -4180,7 +5418,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.783</v>
+        <v>0.839</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4195,11 +5433,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>of 30 (entity-free questions excluded)</t>
+          <t>of 40 (entity-free questions excluded)</t>
         </is>
       </c>
     </row>
@@ -4210,11 +5448,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Q004; Q012; Q013; Q019; Q025; Q029</t>
+          <t>Q004; Q012; Q013; Q019; Q025; Q029; Q033</t>
         </is>
       </c>
     </row>
@@ -4225,11 +5463,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>of 24</t>
+          <t>of 33</t>
         </is>
       </c>
     </row>
@@ -4240,11 +5478,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>of 24</t>
+          <t>of 33</t>
         </is>
       </c>
     </row>
@@ -4255,7 +5493,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -4307,10 +5545,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -4320,10 +5558,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -4333,10 +5571,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; IRS_001; LI_001</t>
+          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2533,16 +2533,12 @@
         <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002; UST_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2568,13 +2564,13 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2589,16 +2585,16 @@
         <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; UST_001; WH_002</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; ALB_001; IEA_001; CSIS_001; IRS_001; UST_001; TSLA_001; WH_002</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; ALB_001; IEA_001; CSIS_001; IRS_001; UST_001; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -2655,6 +2651,174 @@
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>USMCA_001; WB_001; IRS_001; WH_002; WTO_004; DHS_001; CASE_002; EU_003; EU_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001; UST_001; WH_002</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; SNE_001; IEA_001; CSIS_001; UST_001; IRS_001; TSLA_001; WH_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>AD/CVD; China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>UST_001; WH_002</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; UST_001; TRD_001; SNE_001; IEA_001; ALB_001; WH_002; EU_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; WH_002; SNE_001; MOFCOM_002; ALB_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3040,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3100,7 +3264,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; NIO_001; XPEV_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -3600,11 +3764,11 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_002; IRS_001; SNE_001</t>
+          <t>TRD_001; DHS_001; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4804,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>EU_003; SNE_001; IRS_001; LI_001</t>
+          <t>EU_003; SNE_001; TRD_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4832,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; SNE_001; IEA_001; IRS_001</t>
+          <t>TSLA_001; EU_003; DHS_001; SNE_001; IEA_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4860,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; UST_001; LI_001</t>
+          <t>TSLA_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5308,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5336,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; TSLA_001; BIS_001; USMCA_001; CASE_002</t>
+          <t>DHS_001; IRS_001; MOFCOM_002; TSLA_001; BIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5364,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SNE_001; EU_003; ALB_001; IRS_001</t>
+          <t>SNE_001; TRD_001; EU_003; ALB_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5392,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; ALB_001; IEA_001; IRS_001</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; ALB_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -5344,8 +5508,260 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>EU_001; EU_003; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; SNE_001; IEA_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AD/CVD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; TRD_001; SNE_001; ALB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>EU_003; IEA_001; EU_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>EU_002; EU_003; SNE_001; MOFCOM_002; ALB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; EU_001; EU_003; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>EU_002; DHS_001; EU_001; EU_003; SNE_001; MOFCOM_002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F95"/>
+  <autoFilter ref="A1:F104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5388,11 +5804,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mean over 33 entity-bearing questions</t>
+          <t>mean over 36 entity-bearing questions</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5834,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5433,11 +5849,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>of 40 (entity-free questions excluded)</t>
+          <t>of 43 (entity-free questions excluded)</t>
         </is>
       </c>
     </row>
@@ -5463,11 +5879,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>of 33</t>
+          <t>of 36</t>
         </is>
       </c>
     </row>
@@ -5478,11 +5894,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>of 33</t>
+          <t>of 36</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5909,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -5545,10 +5961,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -5558,10 +5974,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -5571,10 +5987,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001</t>
+          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; IEA_001; SNE_001; TSLA_001; ALB_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; IEA_001; SNE_001; TSLA_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_005; CASE_006; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_005; CASE_006; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; TRD_003; CSIS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; CSIS_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; CASE_003; DHS_001; TRD_003; WH_002; TRD_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; EU_003; TSLA_001; TRD_001; CASE_001; SNE_001; IRS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; CASE_001; SNE_001; IRS_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; USMCA_001; CASE_008; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; WH_001; TRD_003; CSIS_001; USMCA_001; CASE_008; CASE_010</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; TRD_003; USMCA_001; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; USMCA_001; TRD_003; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002; CASE_009; BIS_001; MOFCOM_001; TSLA_001</t>
+          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002; BIS_001; MOFCOM_001; CASE_009; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; WTO_001; SNE_001</t>
+          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; SNE_001; WTO_001</t>
         </is>
       </c>
     </row>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2369,16 +2369,16 @@
         <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001</t>
+          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001; ITA_001</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; CASE_001</t>
+          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_002; TRD_003; TRD_001; WB_001</t>
+          <t>CASE_007; CASE_002; TRD_003; WB_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; WB_001</t>
+          <t>CASE_010; WH_002; CASE_003; CASE_002; WB_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; TSLA_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; SNE_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; USMCA_001; WH_002; TRD_003; CSIS_001</t>
+          <t>CASE_010; WH_001; USMCA_001; WH_002; CSIS_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; TRD_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_002; CASE_010</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; DHS_001; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; DHS_001; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; TRD_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; EU_003; TRD_001; SNE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; EU_003; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; USMCA_001; WH_001; CASE_010</t>
+          <t>TRD_003; WH_002; CSIS_001; CASE_010; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WH_002; TRD_003; WH_001; CSIS_001; USMCA_001; CASE_010</t>
+          <t>WH_002; WH_001; TRD_003; CSIS_001; USMCA_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; IEA_001; CASE_001</t>
+          <t>WTO_002; WTO_003; IEA_001</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; UST_001; CASE_001</t>
+          <t>WTO_002; WTO_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.842</v>
+        <v>0.839</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/optimized/entity_accuracy.xlsx
+++ b/data/evaluation/optimized/entity_accuracy.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; IEA_001; CASE_008; CASE_007; WB_001; TRD_001; EU_003</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; IEA_001; CASE_008; CASE_007; WB_001; EU_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
         <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>IEA_001; WTO_004</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001</t>
+          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; WTO_004</t>
         </is>
       </c>
     </row>
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -789,16 +789,16 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001</t>
+          <t>DHS_001; WH_002; CASE_001; SNE_001; CASE_010; ALB_001; IEA_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001; CASE_008</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; WH_002; CASE_001; SNE_001; CASE_010; ALB_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; USMCA_001; TRD_001; DHS_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; USMCA_001; CASE_003; TRD_001; DHS_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; CSIS_001; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; USMCA_001; WH_001; WH_002; DHS_001; TRD_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001; MCK_001; WEF_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001; MCK_001; IRS_001; WEF_001; EU_003</t>
+          <t>MOFCOM_005; MOFCOM_003; CNGOV_001; MOFCOM_006; MOFCOM_004; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; DHS_001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; DHS_001; UST_001</t>
+          <t>WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; DHS_001; USMCA_001; WH_001; UST_001; CASE_002</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; DHS_001; USMCA_001; WH_001; CASE_002; ALB_001</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; CASE_001; SNE_001; IRS_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; SNE_001; IRS_001; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; TSLA_001; CASE_008; DHS_001; CASE_003; CASE_007; CASE_004; ALB_001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; TSLA_001; CASE_008; DHS_001; CASE_003; CASE_007; CASE_004; ALB_001</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; USMCA_001; CASE_010; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; DHS_001; EU_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; DHS_001; EU_001</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MOFCOM_006; MCK_001; MOFCOM_005; WTO_003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MOFCOM_006; MCK_001; MOFCOM_005; WTO_003</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; DHS_001; NIO_001; CASE_001; XPEV_001; MOFCOM_002; IRS_001</t>
+          <t>BIS_002; BIS_001; CASE_009; FR_001; DHS_001; NIO_001; CASE_001; XPEV_001; IRS_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; DOC_001; WTO_001; DHS_001</t>
+          <t>DOC_001; CASE_003; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; DOC_001; CASE_003; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
+          <t>IMF_001; WTO_001; WTO_002; CNGOV_001; MOFCOM_005; UNCTAD_001; EU_004; MOFCOM_004; MOFCOM_003; CASE_001</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
+          <t>IMF_001; WTO_001; WTO_002; CNGOV_001; MOFCOM_005; UNCTAD_001; EU_004; MOFCOM_004; MOFCOM_003; CASE_001</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
+          <t>TSLA_001; EU_003; UST_001; WH_002; DHS_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; TRD_001; SNE_001; EU_003; WTO_002; MOFCOM_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; TRD_001; SNE_001; EU_003; WTO_002; MOFCOM_002; IRS_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; SNE_001; WTO_001</t>
+          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; WTO_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001; ITA_001</t>
+          <t>WH_002; IRS_001; DHS_001; WTO_004; SNE_001; ITA_001</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; ITA_001</t>
+          <t>WTO_002; WTO_003; WH_002; IRS_001; DHS_001; UST_001; WTO_004; IEA_001; SNE_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; EU_003; WTO_002; MOFCOM_002; TSLA_001; EU_002</t>
+          <t>WTO_004; IRS_001; DHS_001; EU_001; SNE_001; EU_003; WTO_002; TSLA_001; MOFCOM_002; EU_002</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; TSLA_001; CSIS_001</t>
+          <t>DHS_001; TSLA_001; UST_001</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>WB_001; DHS_001; TRD_001; CASE_002; SNE_001; IEA_001; TSLA_001; ALB_001; EU_003; CSIS_001</t>
+          <t>WB_001; DHS_001; TRD_001; CASE_002; IEA_001; SNE_001; TSLA_001; ALB_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002; EU_002; BIS_001; USMCA_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; WH_002; WTO_004; DHS_001; CASE_002; EU_003; EU_001; EU_002</t>
+          <t>USMCA_001; WB_001; IRS_001; WTO_004; WH_002; DHS_001; EU_003; CASE_002; EU_001; EU_002</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; UST_001; WH_002</t>
+          <t>UST_001; CSIS_001; WH_002</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; SNE_001; IEA_001; CSIS_001; UST_001; IRS_001; TSLA_001; WH_002</t>
+          <t>EU_001; DHS_001; EU_003; SNE_001; UST_001; IEA_001; CSIS_001; IRS_001; TSLA_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>EU_003; CASE_002; DHS_001; UST_001; TRD_001; SNE_001; IEA_001; ALB_001; WH_002; EU_001</t>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; UST_001; IEA_001; SNE_001; ALB_001; EU_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; WH_002; SNE_001; MOFCOM_002; ALB_001; IEA_001</t>
+          <t>EU_002; EU_004; DHS_001; EU_001; WH_002; EU_003; IEA_001; ALB_001; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_008</t>
+          <t>CASE_003; CASE_002; DOC_001</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; USMCA_001; WH_002; CSIS_001; TRD_003</t>
+          <t>CASE_010; USMCA_001; WH_001; WH_002; TRD_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; SNE_001; IRS_001; EU_003</t>
+          <t>MOFCOM_005; MOFCOM_003; CNGOV_001; MOFCOM_006; MOFCOM_004; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; USMCA_001; CASE_002</t>
+          <t>TRD_003; USMCA_001; CASE_002; ALB_001</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; CASE_010; USMCA_001; WH_001</t>
+          <t>TRD_003; WH_002; CSIS_001; USMCA_001; CASE_010; WH_001</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003</t>
+          <t>DOC_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CSIS_001</t>
+          <t>DOC_001; CASE_002; CASE_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001</t>
+          <t>BIS_002; BIS_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001</t>
+          <t>BIS_002; BIS_001; CASE_009; FR_001</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; DHS_001; NIO_001</t>
+          <t>BIS_002; BIS_001; CASE_009; FR_001; DHS_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; EU_003; WTO_002</t>
+          <t>IRS_001; DHS_001; EU_001; SNE_001; EU_003; WTO_002</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; MOFCOM_002; TSLA_001; BIS_001; USMCA_001</t>
+          <t>DHS_001; IRS_001; TSLA_001; MOFCOM_002; BIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; CASE_002; EU_003; EU_002</t>
+          <t>USMCA_001; WB_001; IRS_001; EU_003; CASE_002; EU_002</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>WB_001; WH_002; WTO_004</t>
+          <t>WB_001; WTO_004; WH_002</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IEA_001</t>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; IEA_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EU_002; EU_003; SNE_001; MOFCOM_002; ALB_001</t>
+          <t>EU_002; EU_003; ALB_001; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EU_002; DHS_001; EU_001; EU_003; SNE_001; MOFCOM_002</t>
+          <t>EU_002; DHS_001; EU_001; EU_003; IEA_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
